--- a/testing/Broadcasting_Testing_Plan.xlsx
+++ b/testing/Broadcasting_Testing_Plan.xlsx
@@ -1428,10 +1428,10 @@
         <v>24.25</v>
       </c>
       <c r="C3" t="str">
-        <v>0</v>
+        <v>24.25</v>
       </c>
       <c r="D3" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="E3" t="str">
         <v>Super on 7.5hr ordinary Cinema L1</v>
